--- a/testing/glm-mv-reference/spss-output/mv4_one_way.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv4_one_way.xlsx
@@ -1018,88 +1018,88 @@
   </cellXfs>
   <cellStyles count="83">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1790153298871" xfId="1"/>
-    <cellStyle name="style1790153298940" xfId="2"/>
-    <cellStyle name="style1790153298958" xfId="3"/>
-    <cellStyle name="style1790153298986" xfId="4"/>
-    <cellStyle name="style1790153299002" xfId="5"/>
-    <cellStyle name="style1790153299030" xfId="6"/>
-    <cellStyle name="style1790153299045" xfId="7"/>
-    <cellStyle name="style1790153299068" xfId="8"/>
-    <cellStyle name="style1790153299087" xfId="9"/>
-    <cellStyle name="style1790153299105" xfId="10"/>
-    <cellStyle name="style1790153299126" xfId="11"/>
-    <cellStyle name="style1790153299148" xfId="12"/>
-    <cellStyle name="style1790153299167" xfId="13"/>
-    <cellStyle name="style1790153299188" xfId="14"/>
-    <cellStyle name="style1790153299211" xfId="15"/>
-    <cellStyle name="style1790153299224" xfId="16"/>
-    <cellStyle name="style1790153299240" xfId="17"/>
-    <cellStyle name="style1790153299258" xfId="18"/>
-    <cellStyle name="style1790153299281" xfId="19"/>
-    <cellStyle name="style1790153299299" xfId="20"/>
-    <cellStyle name="style1790153299318" xfId="21"/>
-    <cellStyle name="style1790153299339" xfId="22"/>
-    <cellStyle name="style1790153299349" xfId="23"/>
-    <cellStyle name="style1790153299365" xfId="24"/>
-    <cellStyle name="style1790153299385" xfId="25"/>
-    <cellStyle name="style1790153299406" xfId="26"/>
-    <cellStyle name="style1790153299425" xfId="27"/>
-    <cellStyle name="style1790153299449" xfId="28"/>
-    <cellStyle name="style1790153299468" xfId="29"/>
-    <cellStyle name="style1790153299489" xfId="30"/>
-    <cellStyle name="style1790153299512" xfId="31"/>
-    <cellStyle name="style1790153299533" xfId="32"/>
-    <cellStyle name="style1790153299552" xfId="33"/>
-    <cellStyle name="style1790153299574" xfId="34"/>
-    <cellStyle name="style1790153299592" xfId="35"/>
-    <cellStyle name="style1790153299614" xfId="36"/>
-    <cellStyle name="style1790153299628" xfId="37"/>
-    <cellStyle name="style1790153299648" xfId="38"/>
-    <cellStyle name="style1790153299661" xfId="39"/>
-    <cellStyle name="style1790153299683" xfId="40"/>
-    <cellStyle name="style1790153299703" xfId="41"/>
-    <cellStyle name="style1790153299726" xfId="42"/>
-    <cellStyle name="style1790153299747" xfId="43"/>
-    <cellStyle name="style1790153299759" xfId="44"/>
-    <cellStyle name="style1790153299780" xfId="45"/>
-    <cellStyle name="style1790153299793" xfId="46"/>
-    <cellStyle name="style1790153299809" xfId="47"/>
-    <cellStyle name="style1790153299823" xfId="48"/>
-    <cellStyle name="style1790153299838" xfId="49"/>
-    <cellStyle name="style1790153299851" xfId="50"/>
-    <cellStyle name="style1790153299867" xfId="51"/>
-    <cellStyle name="style1790153299886" xfId="52"/>
-    <cellStyle name="style1790153299903" xfId="53"/>
-    <cellStyle name="style1790153299917" xfId="54"/>
-    <cellStyle name="style1790153299936" xfId="55"/>
-    <cellStyle name="style1790153299949" xfId="56"/>
-    <cellStyle name="style1790153299977" xfId="57"/>
-    <cellStyle name="style1790153299993" xfId="58"/>
-    <cellStyle name="style1790153300008" xfId="59"/>
-    <cellStyle name="style1790153300023" xfId="60"/>
-    <cellStyle name="style1790153300037" xfId="61"/>
-    <cellStyle name="style1790153300051" xfId="62"/>
-    <cellStyle name="style1790153300066" xfId="63"/>
-    <cellStyle name="style1790153300079" xfId="64"/>
-    <cellStyle name="style1790153300091" xfId="65"/>
-    <cellStyle name="style1790153300106" xfId="66"/>
-    <cellStyle name="style1790153300123" xfId="67"/>
-    <cellStyle name="style1790153300132" xfId="68"/>
-    <cellStyle name="style1790153300151" xfId="69"/>
-    <cellStyle name="style1790153300178" xfId="70"/>
-    <cellStyle name="style1790153300193" xfId="71"/>
-    <cellStyle name="style1790153300208" xfId="72"/>
-    <cellStyle name="style1790153300223" xfId="73"/>
-    <cellStyle name="style1790153300239" xfId="74"/>
-    <cellStyle name="style1790153300259" xfId="75"/>
-    <cellStyle name="style1790153300273" xfId="76"/>
-    <cellStyle name="style1790153300289" xfId="77"/>
-    <cellStyle name="style1790153300301" xfId="78"/>
-    <cellStyle name="style1790153300318" xfId="79"/>
-    <cellStyle name="style1790153300332" xfId="80"/>
-    <cellStyle name="style1790153300347" xfId="81"/>
-    <cellStyle name="style1790153300360" xfId="82"/>
+    <cellStyle name="style1791326362801" xfId="1"/>
+    <cellStyle name="style1791326362868" xfId="2"/>
+    <cellStyle name="style1791326362896" xfId="3"/>
+    <cellStyle name="style1791326362931" xfId="4"/>
+    <cellStyle name="style1791326362964" xfId="5"/>
+    <cellStyle name="style1791326362999" xfId="6"/>
+    <cellStyle name="style1791326363022" xfId="7"/>
+    <cellStyle name="style1791326363058" xfId="8"/>
+    <cellStyle name="style1791326363090" xfId="9"/>
+    <cellStyle name="style1791326363121" xfId="10"/>
+    <cellStyle name="style1791326363156" xfId="11"/>
+    <cellStyle name="style1791326363187" xfId="12"/>
+    <cellStyle name="style1791326363216" xfId="13"/>
+    <cellStyle name="style1791326363249" xfId="14"/>
+    <cellStyle name="style1791326363279" xfId="15"/>
+    <cellStyle name="style1791326363303" xfId="16"/>
+    <cellStyle name="style1791326363325" xfId="17"/>
+    <cellStyle name="style1791326363354" xfId="18"/>
+    <cellStyle name="style1791326363383" xfId="19"/>
+    <cellStyle name="style1791326363413" xfId="20"/>
+    <cellStyle name="style1791326363438" xfId="21"/>
+    <cellStyle name="style1791326363467" xfId="22"/>
+    <cellStyle name="style1791326363488" xfId="23"/>
+    <cellStyle name="style1791326363509" xfId="24"/>
+    <cellStyle name="style1791326363528" xfId="25"/>
+    <cellStyle name="style1791326363553" xfId="26"/>
+    <cellStyle name="style1791326363580" xfId="27"/>
+    <cellStyle name="style1791326363605" xfId="28"/>
+    <cellStyle name="style1791326363629" xfId="29"/>
+    <cellStyle name="style1791326363656" xfId="30"/>
+    <cellStyle name="style1791326363684" xfId="31"/>
+    <cellStyle name="style1791326363712" xfId="32"/>
+    <cellStyle name="style1791326363739" xfId="33"/>
+    <cellStyle name="style1791326363766" xfId="34"/>
+    <cellStyle name="style1791326363795" xfId="35"/>
+    <cellStyle name="style1791326363826" xfId="36"/>
+    <cellStyle name="style1791326363846" xfId="37"/>
+    <cellStyle name="style1791326363874" xfId="38"/>
+    <cellStyle name="style1791326363895" xfId="39"/>
+    <cellStyle name="style1791326363925" xfId="40"/>
+    <cellStyle name="style1791326363954" xfId="41"/>
+    <cellStyle name="style1791326363982" xfId="42"/>
+    <cellStyle name="style1791326364014" xfId="43"/>
+    <cellStyle name="style1791326364039" xfId="44"/>
+    <cellStyle name="style1791326364067" xfId="45"/>
+    <cellStyle name="style1791326364088" xfId="46"/>
+    <cellStyle name="style1791326364109" xfId="47"/>
+    <cellStyle name="style1791326364128" xfId="48"/>
+    <cellStyle name="style1791326364150" xfId="49"/>
+    <cellStyle name="style1791326364169" xfId="50"/>
+    <cellStyle name="style1791326364191" xfId="51"/>
+    <cellStyle name="style1791326364219" xfId="52"/>
+    <cellStyle name="style1791326364246" xfId="53"/>
+    <cellStyle name="style1791326364269" xfId="54"/>
+    <cellStyle name="style1791326364296" xfId="55"/>
+    <cellStyle name="style1791326364325" xfId="56"/>
+    <cellStyle name="style1791326364352" xfId="57"/>
+    <cellStyle name="style1791326364373" xfId="58"/>
+    <cellStyle name="style1791326364393" xfId="59"/>
+    <cellStyle name="style1791326364414" xfId="60"/>
+    <cellStyle name="style1791326364432" xfId="61"/>
+    <cellStyle name="style1791326364450" xfId="62"/>
+    <cellStyle name="style1791326364472" xfId="63"/>
+    <cellStyle name="style1791326364489" xfId="64"/>
+    <cellStyle name="style1791326364509" xfId="65"/>
+    <cellStyle name="style1791326364529" xfId="66"/>
+    <cellStyle name="style1791326364545" xfId="67"/>
+    <cellStyle name="style1791326364564" xfId="68"/>
+    <cellStyle name="style1791326364582" xfId="69"/>
+    <cellStyle name="style1791326364622" xfId="70"/>
+    <cellStyle name="style1791326364644" xfId="71"/>
+    <cellStyle name="style1791326364667" xfId="72"/>
+    <cellStyle name="style1791326364687" xfId="73"/>
+    <cellStyle name="style1791326364714" xfId="74"/>
+    <cellStyle name="style1791326364745" xfId="75"/>
+    <cellStyle name="style1791326364763" xfId="76"/>
+    <cellStyle name="style1791326364786" xfId="77"/>
+    <cellStyle name="style1791326364808" xfId="78"/>
+    <cellStyle name="style1791326364828" xfId="79"/>
+    <cellStyle name="style1791326364845" xfId="80"/>
+    <cellStyle name="style1791326364868" xfId="81"/>
+    <cellStyle name="style1791326364889" xfId="82"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1504,7 +1504,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>23-SEP-2026 15:48:18</t>
+          <t>07-OCT-2026 05:39:22</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.00</t>
+          <t>00:00:00.03</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>00:00:00.01</t>
+          <t>00:00:00.02</t>
         </is>
       </c>
     </row>

--- a/testing/glm-mv-reference/spss-output/mv4_one_way.xlsx
+++ b/testing/glm-mv-reference/spss-output/mv4_one_way.xlsx
@@ -1018,88 +1018,88 @@
   </cellXfs>
   <cellStyles count="83">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="style1791326362801" xfId="1"/>
-    <cellStyle name="style1791326362868" xfId="2"/>
-    <cellStyle name="style1791326362896" xfId="3"/>
-    <cellStyle name="style1791326362931" xfId="4"/>
-    <cellStyle name="style1791326362964" xfId="5"/>
-    <cellStyle name="style1791326362999" xfId="6"/>
-    <cellStyle name="style1791326363022" xfId="7"/>
-    <cellStyle name="style1791326363058" xfId="8"/>
-    <cellStyle name="style1791326363090" xfId="9"/>
-    <cellStyle name="style1791326363121" xfId="10"/>
-    <cellStyle name="style1791326363156" xfId="11"/>
-    <cellStyle name="style1791326363187" xfId="12"/>
-    <cellStyle name="style1791326363216" xfId="13"/>
-    <cellStyle name="style1791326363249" xfId="14"/>
-    <cellStyle name="style1791326363279" xfId="15"/>
-    <cellStyle name="style1791326363303" xfId="16"/>
-    <cellStyle name="style1791326363325" xfId="17"/>
-    <cellStyle name="style1791326363354" xfId="18"/>
-    <cellStyle name="style1791326363383" xfId="19"/>
-    <cellStyle name="style1791326363413" xfId="20"/>
-    <cellStyle name="style1791326363438" xfId="21"/>
-    <cellStyle name="style1791326363467" xfId="22"/>
-    <cellStyle name="style1791326363488" xfId="23"/>
-    <cellStyle name="style1791326363509" xfId="24"/>
-    <cellStyle name="style1791326363528" xfId="25"/>
-    <cellStyle name="style1791326363553" xfId="26"/>
-    <cellStyle name="style1791326363580" xfId="27"/>
-    <cellStyle name="style1791326363605" xfId="28"/>
-    <cellStyle name="style1791326363629" xfId="29"/>
-    <cellStyle name="style1791326363656" xfId="30"/>
-    <cellStyle name="style1791326363684" xfId="31"/>
-    <cellStyle name="style1791326363712" xfId="32"/>
-    <cellStyle name="style1791326363739" xfId="33"/>
-    <cellStyle name="style1791326363766" xfId="34"/>
-    <cellStyle name="style1791326363795" xfId="35"/>
-    <cellStyle name="style1791326363826" xfId="36"/>
-    <cellStyle name="style1791326363846" xfId="37"/>
-    <cellStyle name="style1791326363874" xfId="38"/>
-    <cellStyle name="style1791326363895" xfId="39"/>
-    <cellStyle name="style1791326363925" xfId="40"/>
-    <cellStyle name="style1791326363954" xfId="41"/>
-    <cellStyle name="style1791326363982" xfId="42"/>
-    <cellStyle name="style1791326364014" xfId="43"/>
-    <cellStyle name="style1791326364039" xfId="44"/>
-    <cellStyle name="style1791326364067" xfId="45"/>
-    <cellStyle name="style1791326364088" xfId="46"/>
-    <cellStyle name="style1791326364109" xfId="47"/>
-    <cellStyle name="style1791326364128" xfId="48"/>
-    <cellStyle name="style1791326364150" xfId="49"/>
-    <cellStyle name="style1791326364169" xfId="50"/>
-    <cellStyle name="style1791326364191" xfId="51"/>
-    <cellStyle name="style1791326364219" xfId="52"/>
-    <cellStyle name="style1791326364246" xfId="53"/>
-    <cellStyle name="style1791326364269" xfId="54"/>
-    <cellStyle name="style1791326364296" xfId="55"/>
-    <cellStyle name="style1791326364325" xfId="56"/>
-    <cellStyle name="style1791326364352" xfId="57"/>
-    <cellStyle name="style1791326364373" xfId="58"/>
-    <cellStyle name="style1791326364393" xfId="59"/>
-    <cellStyle name="style1791326364414" xfId="60"/>
-    <cellStyle name="style1791326364432" xfId="61"/>
-    <cellStyle name="style1791326364450" xfId="62"/>
-    <cellStyle name="style1791326364472" xfId="63"/>
-    <cellStyle name="style1791326364489" xfId="64"/>
-    <cellStyle name="style1791326364509" xfId="65"/>
-    <cellStyle name="style1791326364529" xfId="66"/>
-    <cellStyle name="style1791326364545" xfId="67"/>
-    <cellStyle name="style1791326364564" xfId="68"/>
-    <cellStyle name="style1791326364582" xfId="69"/>
-    <cellStyle name="style1791326364622" xfId="70"/>
-    <cellStyle name="style1791326364644" xfId="71"/>
-    <cellStyle name="style1791326364667" xfId="72"/>
-    <cellStyle name="style1791326364687" xfId="73"/>
-    <cellStyle name="style1791326364714" xfId="74"/>
-    <cellStyle name="style1791326364745" xfId="75"/>
-    <cellStyle name="style1791326364763" xfId="76"/>
-    <cellStyle name="style1791326364786" xfId="77"/>
-    <cellStyle name="style1791326364808" xfId="78"/>
-    <cellStyle name="style1791326364828" xfId="79"/>
-    <cellStyle name="style1791326364845" xfId="80"/>
-    <cellStyle name="style1791326364868" xfId="81"/>
-    <cellStyle name="style1791326364889" xfId="82"/>
+    <cellStyle name="style1790153298871" xfId="1"/>
+    <cellStyle name="style1790153298940" xfId="2"/>
+    <cellStyle name="style1790153298958" xfId="3"/>
+    <cellStyle name="style1790153298986" xfId="4"/>
+    <cellStyle name="style1790153299002" xfId="5"/>
+    <cellStyle name="style1790153299030" xfId="6"/>
+    <cellStyle name="style1790153299045" xfId="7"/>
+    <cellStyle name="style1790153299068" xfId="8"/>
+    <cellStyle name="style1790153299087" xfId="9"/>
+    <cellStyle name="style1790153299105" xfId="10"/>
+    <cellStyle name="style1790153299126" xfId="11"/>
+    <cellStyle name="style1790153299148" xfId="12"/>
+    <cellStyle name="style1790153299167" xfId="13"/>
+    <cellStyle name="style1790153299188" xfId="14"/>
+    <cellStyle name="style1790153299211" xfId="15"/>
+    <cellStyle name="style1790153299224" xfId="16"/>
+    <cellStyle name="style1790153299240" xfId="17"/>
+    <cellStyle name="style1790153299258" xfId="18"/>
+    <cellStyle name="style1790153299281" xfId="19"/>
+    <cellStyle name="style1790153299299" xfId="20"/>
+    <cellStyle name="style1790153299318" xfId="21"/>
+    <cellStyle name="style1790153299339" xfId="22"/>
+    <cellStyle name="style1790153299349" xfId="23"/>
+    <cellStyle name="style1790153299365" xfId="24"/>
+    <cellStyle name="style1790153299385" xfId="25"/>
+    <cellStyle name="style1790153299406" xfId="26"/>
+    <cellStyle name="style1790153299425" xfId="27"/>
+    <cellStyle name="style1790153299449" xfId="28"/>
+    <cellStyle name="style1790153299468" xfId="29"/>
+    <cellStyle name="style1790153299489" xfId="30"/>
+    <cellStyle name="style1790153299512" xfId="31"/>
+    <cellStyle name="style1790153299533" xfId="32"/>
+    <cellStyle name="style1790153299552" xfId="33"/>
+    <cellStyle name="style1790153299574" xfId="34"/>
+    <cellStyle name="style1790153299592" xfId="35"/>
+    <cellStyle name="style1790153299614" xfId="36"/>
+    <cellStyle name="style1790153299628" xfId="37"/>
+    <cellStyle name="style1790153299648" xfId="38"/>
+    <cellStyle name="style1790153299661" xfId="39"/>
+    <cellStyle name="style1790153299683" xfId="40"/>
+    <cellStyle name="style1790153299703" xfId="41"/>
+    <cellStyle name="style1790153299726" xfId="42"/>
+    <cellStyle name="style1790153299747" xfId="43"/>
+    <cellStyle name="style1790153299759" xfId="44"/>
+    <cellStyle name="style1790153299780" xfId="45"/>
+    <cellStyle name="style1790153299793" xfId="46"/>
+    <cellStyle name="style1790153299809" xfId="47"/>
+    <cellStyle name="style1790153299823" xfId="48"/>
+    <cellStyle name="style1790153299838" xfId="49"/>
+    <cellStyle name="style1790153299851" xfId="50"/>
+    <cellStyle name="style1790153299867" xfId="51"/>
+    <cellStyle name="style1790153299886" xfId="52"/>
+    <cellStyle name="style1790153299903" xfId="53"/>
+    <cellStyle name="style1790153299917" xfId="54"/>
+    <cellStyle name="style1790153299936" xfId="55"/>
+    <cellStyle name="style1790153299949" xfId="56"/>
+    <cellStyle name="style1790153299977" xfId="57"/>
+    <cellStyle name="style1790153299993" xfId="58"/>
+    <cellStyle name="style1790153300008" xfId="59"/>
+    <cellStyle name="style1790153300023" xfId="60"/>
+    <cellStyle name="style1790153300037" xfId="61"/>
+    <cellStyle name="style1790153300051" xfId="62"/>
+    <cellStyle name="style1790153300066" xfId="63"/>
+    <cellStyle name="style1790153300079" xfId="64"/>
+    <cellStyle name="style1790153300091" xfId="65"/>
+    <cellStyle name="style1790153300106" xfId="66"/>
+    <cellStyle name="style1790153300123" xfId="67"/>
+    <cellStyle name="style1790153300132" xfId="68"/>
+    <cellStyle name="style1790153300151" xfId="69"/>
+    <cellStyle name="style1790153300178" xfId="70"/>
+    <cellStyle name="style1790153300193" xfId="71"/>
+    <cellStyle name="style1790153300208" xfId="72"/>
+    <cellStyle name="style1790153300223" xfId="73"/>
+    <cellStyle name="style1790153300239" xfId="74"/>
+    <cellStyle name="style1790153300259" xfId="75"/>
+    <cellStyle name="style1790153300273" xfId="76"/>
+    <cellStyle name="style1790153300289" xfId="77"/>
+    <cellStyle name="style1790153300301" xfId="78"/>
+    <cellStyle name="style1790153300318" xfId="79"/>
+    <cellStyle name="style1790153300332" xfId="80"/>
+    <cellStyle name="style1790153300347" xfId="81"/>
+    <cellStyle name="style1790153300360" xfId="82"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1504,7 +1504,7 @@
       <c r="B18" s="8"/>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>07-OCT-2026 05:39:22</t>
+          <t>23-SEP-2026 15:48:18</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>00:00:00.03</t>
+          <t>00:00:00.00</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>00:00:00.02</t>
+          <t>00:00:00.01</t>
         </is>
       </c>
     </row>
